--- a/1-code/ruwen/figure/network_table_m.xlsx
+++ b/1-code/ruwen/figure/network_table_m.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qd/Desktop/helios/HELIOS-project/1-code/ruwen/figure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{361AB124-E981-F94B-950A-68BF888D4D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2B5BC69-3397-9348-A7BA-4C915D00C238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="27920" windowHeight="17960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="800" yWindow="500" windowWidth="27920" windowHeight="16360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2569" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2569" uniqueCount="331">
   <si>
     <t>from</t>
   </si>
@@ -1010,6 +1010,10 @@
   </si>
   <si>
     <t>Zinc</t>
+  </si>
+  <si>
+    <t>Klebsiella quasipneumoniae</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1045,12 +1049,18 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1065,12 +1075,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -9563,264 +9574,264 @@
         <v>3.020006113381108</v>
       </c>
     </row>
-    <row r="283" spans="1:9">
-      <c r="A283" s="2" t="s">
+    <row r="283" spans="1:9" s="3" customFormat="1">
+      <c r="A283" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="B283" s="2" t="s">
+      <c r="B283" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="C283" s="2">
+      <c r="C283" s="3">
         <v>-0.51379281084005501</v>
       </c>
-      <c r="D283" s="2">
+      <c r="D283" s="3">
         <v>5.1661546409041779E-3</v>
       </c>
-      <c r="E283" s="2" t="s">
+      <c r="E283" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="F283" s="2" t="s">
+      <c r="F283" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="G283" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H283" s="2">
+      <c r="G283" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H283" s="3">
         <v>0.51379281084005501</v>
       </c>
-      <c r="I283" s="2">
+      <c r="I283" s="3">
         <v>2.286832598029874</v>
       </c>
     </row>
-    <row r="284" spans="1:9">
-      <c r="A284" s="2" t="s">
+    <row r="284" spans="1:9" s="3" customFormat="1">
+      <c r="A284" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="B284" s="2" t="s">
+      <c r="B284" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="C284" s="2">
+      <c r="C284" s="3">
         <v>-0.45601081080907441</v>
       </c>
-      <c r="D284" s="2">
+      <c r="D284" s="3">
         <v>1.5571526927386659E-2</v>
       </c>
-      <c r="E284" s="2" t="s">
+      <c r="E284" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="F284" s="2" t="s">
+      <c r="F284" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="G284" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H284" s="2">
+      <c r="G284" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H284" s="3">
         <v>0.45601081080907441</v>
       </c>
-      <c r="I284" s="2">
+      <c r="I284" s="3">
         <v>1.8076687988882689</v>
       </c>
     </row>
-    <row r="285" spans="1:9">
-      <c r="A285" s="2" t="s">
+    <row r="285" spans="1:9" s="3" customFormat="1">
+      <c r="A285" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="B285" s="2" t="s">
+      <c r="B285" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="C285" s="2">
+      <c r="C285" s="3">
         <v>-0.47972806011941688</v>
       </c>
-      <c r="D285" s="2">
+      <c r="D285" s="3">
         <v>1.014522486157788E-2</v>
       </c>
-      <c r="E285" s="2" t="s">
+      <c r="E285" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="F285" s="2" t="s">
+      <c r="F285" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="G285" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H285" s="2">
+      <c r="G285" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H285" s="3">
         <v>0.47972806011941688</v>
       </c>
-      <c r="I285" s="2">
+      <c r="I285" s="3">
         <v>1.9937383227005989</v>
       </c>
     </row>
-    <row r="286" spans="1:9">
-      <c r="A286" s="2" t="s">
+    <row r="286" spans="1:9" s="3" customFormat="1">
+      <c r="A286" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="B286" s="2" t="s">
+      <c r="B286" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="C286" s="2">
+      <c r="C286" s="3">
         <v>-0.51148774519551876</v>
       </c>
-      <c r="D286" s="2">
+      <c r="D286" s="3">
         <v>5.4123472710781032E-3</v>
       </c>
-      <c r="E286" s="2" t="s">
+      <c r="E286" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="F286" s="2" t="s">
+      <c r="F286" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="G286" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H286" s="2">
+      <c r="G286" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H286" s="3">
         <v>0.51148774519551876</v>
       </c>
-      <c r="I286" s="2">
+      <c r="I286" s="3">
         <v>2.2666143456526862</v>
       </c>
     </row>
-    <row r="287" spans="1:9">
-      <c r="A287" s="2" t="s">
+    <row r="287" spans="1:9" s="3" customFormat="1">
+      <c r="A287" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="B287" s="2" t="s">
+      <c r="B287" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="C287" s="2">
+      <c r="C287" s="3">
         <v>-0.50374265357540449</v>
       </c>
-      <c r="D287" s="2">
+      <c r="D287" s="3">
         <v>6.3412080666211384E-3</v>
       </c>
-      <c r="E287" s="2" t="s">
+      <c r="E287" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="F287" s="2" t="s">
+      <c r="F287" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="G287" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H287" s="2">
+      <c r="G287" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H287" s="3">
         <v>0.50374265357540449</v>
       </c>
-      <c r="I287" s="2">
+      <c r="I287" s="3">
         <v>2.197827996583904</v>
       </c>
     </row>
-    <row r="288" spans="1:9">
-      <c r="A288" s="2" t="s">
+    <row r="288" spans="1:9" s="3" customFormat="1">
+      <c r="A288" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B288" s="2" t="s">
+      <c r="B288" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="C288" s="2">
+      <c r="C288" s="3">
         <v>-0.51223048436685503</v>
       </c>
-      <c r="D288" s="2">
+      <c r="D288" s="3">
         <v>5.3319597494353374E-3</v>
       </c>
-      <c r="E288" s="2" t="s">
+      <c r="E288" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="F288" s="2" t="s">
+      <c r="F288" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="G288" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H288" s="2">
+      <c r="G288" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H288" s="3">
         <v>0.51223048436685503</v>
       </c>
-      <c r="I288" s="2">
+      <c r="I288" s="3">
         <v>2.2731131377023091</v>
       </c>
     </row>
-    <row r="289" spans="1:9">
-      <c r="A289" s="2" t="s">
+    <row r="289" spans="1:9" s="3" customFormat="1">
+      <c r="A289" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="B289" s="2" t="s">
+      <c r="B289" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="C289" s="2">
+      <c r="C289" s="3">
         <v>-0.45320974136706887</v>
       </c>
-      <c r="D289" s="2">
+      <c r="D289" s="3">
         <v>1.635554867003499E-2</v>
       </c>
-      <c r="E289" s="2" t="s">
+      <c r="E289" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="F289" s="2" t="s">
+      <c r="F289" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="G289" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H289" s="2">
+      <c r="G289" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H289" s="3">
         <v>0.45320974136706887</v>
       </c>
-      <c r="I289" s="2">
+      <c r="I289" s="3">
         <v>1.7863348822713909</v>
       </c>
     </row>
-    <row r="290" spans="1:9">
-      <c r="A290" s="2" t="s">
+    <row r="290" spans="1:9" s="3" customFormat="1">
+      <c r="A290" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="B290" s="2" t="s">
+      <c r="B290" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="C290" s="2">
+      <c r="C290" s="3">
         <v>-0.45011485621259639</v>
       </c>
-      <c r="D290" s="2">
+      <c r="D290" s="3">
         <v>1.7251486175732481E-2</v>
       </c>
-      <c r="E290" s="2" t="s">
+      <c r="E290" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="F290" s="2" t="s">
+      <c r="F290" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="G290" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H290" s="2">
+      <c r="G290" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H290" s="3">
         <v>0.45011485621259639</v>
       </c>
-      <c r="I290" s="2">
+      <c r="I290" s="3">
         <v>1.763173485511434</v>
       </c>
     </row>
-    <row r="291" spans="1:9">
-      <c r="A291" s="2" t="s">
+    <row r="291" spans="1:9" s="3" customFormat="1">
+      <c r="A291" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="B291" s="2" t="s">
+      <c r="B291" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="C291" s="2">
+      <c r="C291" s="3">
         <v>-0.45044732867071308</v>
       </c>
-      <c r="D291" s="2">
+      <c r="D291" s="3">
         <v>1.7153581590564269E-2</v>
       </c>
-      <c r="E291" s="2" t="s">
+      <c r="E291" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="F291" s="2" t="s">
+      <c r="F291" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="G291" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H291" s="2">
+      <c r="G291" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H291" s="3">
         <v>0.45044732867071308</v>
       </c>
-      <c r="I291" s="2">
+      <c r="I291" s="3">
         <v>1.7656451874217849</v>
       </c>
     </row>
@@ -12666,32 +12677,32 @@
         <v>2.244153518490386</v>
       </c>
     </row>
-    <row r="390" spans="1:9">
-      <c r="A390" s="2" t="s">
+    <row r="390" spans="1:9" s="3" customFormat="1">
+      <c r="A390" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="B390" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="C390" s="3">
+        <v>-0.44904370245755548</v>
+      </c>
+      <c r="D390" s="3">
+        <v>1.7573356595737149E-2</v>
+      </c>
+      <c r="E390" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="B390" s="2" t="s">
+      <c r="F390" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="C390" s="2">
-        <v>-0.44904370245755548</v>
-      </c>
-      <c r="D390" s="2">
-        <v>1.7573356595737149E-2</v>
-      </c>
-      <c r="E390" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="F390" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="G390" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H390" s="2">
+      <c r="G390" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H390" s="3">
         <v>0.44904370245755548</v>
       </c>
-      <c r="I390" s="2">
+      <c r="I390" s="3">
         <v>1.7551452782440891</v>
       </c>
     </row>
